--- a/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 10,42</t>
+          <t>-9,56; 9,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 1,55</t>
+          <t>-14,6; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,7; 6,52</t>
+          <t>-15,99; 6,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 8,68</t>
+          <t>-20,31; 7,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 46,6</t>
+          <t>-29,62; 40,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 1,73</t>
+          <t>-16,04; 1,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 8,94</t>
+          <t>-20,39; 8,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 29,88</t>
+          <t>-40,54; 23,45</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 10,36</t>
+          <t>-8,51; 9,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 8,5</t>
+          <t>-6,51; 8,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,8; -0,76</t>
+          <t>-16,21; -0,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 3,11</t>
+          <t>-15,26; 2,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,1; 42,2</t>
+          <t>-24,86; 38,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 11,12</t>
+          <t>-7,76; 11,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,47; -1,09</t>
+          <t>-19,85; -0,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,68; 7,77</t>
+          <t>-31,01; 7,17</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 7,9</t>
+          <t>-11,31; 7,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 4,71</t>
+          <t>-10,64; 4,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 12,0</t>
+          <t>-7,87; 12,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 7,62</t>
+          <t>-9,66; 7,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,67; 29,23</t>
+          <t>-32,07; 31,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 5,28</t>
+          <t>-11,72; 5,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 24,84</t>
+          <t>-13,11; 24,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,43; 42,92</t>
+          <t>-41,95; 42,32</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 12,41</t>
+          <t>-4,99; 13,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 9,5</t>
+          <t>-5,29; 9,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 12,11</t>
+          <t>-6,02; 11,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 9,54</t>
+          <t>-7,72; 9,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 45,72</t>
+          <t>-14,0; 45,1</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 12,36</t>
+          <t>-6,53; 12,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 18,27</t>
+          <t>-8,17; 16,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 35,67</t>
+          <t>-21,98; 36,36</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,27</t>
+          <t>-3,61; 5,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,61</t>
+          <t>-4,95; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 2,75</t>
+          <t>-6,14; 2,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 1,95</t>
+          <t>-8,85; 1,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 18,98</t>
+          <t>-10,71; 21,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 3,13</t>
+          <t>-5,83; 3,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 4,09</t>
+          <t>-8,56; 4,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 6,15</t>
+          <t>-24,84; 5,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 9,21</t>
+          <t>-9,73; 10,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 1,31</t>
+          <t>-15,07; 1,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 6,09</t>
+          <t>-16,1; 6,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 7,3</t>
+          <t>-20,12; 8,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 40,35</t>
+          <t>-30,12; 46,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,04; 1,56</t>
+          <t>-16,27; 1,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 8,67</t>
+          <t>-19,9; 9,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,54; 23,45</t>
+          <t>-40,78; 27,7</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 9,48</t>
+          <t>-8,79; 8,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 8,69</t>
+          <t>-6,67; 8,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,21; -0,36</t>
+          <t>-16,14; -0,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 2,86</t>
+          <t>-14,32; 2,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 38,19</t>
+          <t>-26,29; 35,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 11,2</t>
+          <t>-7,79; 11,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,85; -0,19</t>
+          <t>-19,56; -0,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,01; 7,17</t>
+          <t>-30,23; 7,01</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 7,8</t>
+          <t>-11,96; 7,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 4,71</t>
+          <t>-9,86; 4,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 12,1</t>
+          <t>-8,72; 12,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 7,36</t>
+          <t>-11,62; 7,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 31,26</t>
+          <t>-31,98; 29,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 5,78</t>
+          <t>-11,01; 5,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 24,51</t>
+          <t>-15,06; 25,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,95; 42,32</t>
+          <t>-46,99; 44,88</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 13,08</t>
+          <t>-4,72; 12,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 9,1</t>
+          <t>-5,87; 9,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 11,03</t>
+          <t>-6,17; 11,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 9,55</t>
+          <t>-9,11; 9,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 45,1</t>
+          <t>-12,33; 44,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 12,09</t>
+          <t>-6,91; 12,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 16,25</t>
+          <t>-8,0; 17,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 36,36</t>
+          <t>-24,49; 35,98</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 5,98</t>
+          <t>-2,73; 6,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 2,55</t>
+          <t>-4,89; 2,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 2,94</t>
+          <t>-6,41; 3,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 1,72</t>
+          <t>-8,76; 1,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,71; 21,73</t>
+          <t>-8,18; 21,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,13</t>
+          <t>-5,7; 3,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 4,51</t>
+          <t>-9,01; 4,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 5,18</t>
+          <t>-23,91; 4,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2B_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-4,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-8,31%</t>
+          <t>-11,49%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 10,5</t>
+          <t>-9,12; 10,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 1,26</t>
+          <t>-15,04; 1,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 6,44</t>
+          <t>-16,7; 6,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,12; 8,31</t>
+          <t>-18,26; 5,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 46,61</t>
+          <t>-28,7; 46,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 1,5</t>
+          <t>-16,43; 1,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 9,1</t>
+          <t>-20,67; 8,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,78; 27,7</t>
+          <t>-38,06; 18,56</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,26</t>
+          <t>-8,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-13,93%</t>
+          <t>-19,47%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 8,94</t>
+          <t>-7,68; 10,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 8,52</t>
+          <t>-5,94; 8,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-16,14; -0,6</t>
+          <t>-15,8; -0,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 2,96</t>
+          <t>-18,17; -0,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 35,75</t>
+          <t>-23,1; 42,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 11,13</t>
+          <t>-7,06; 11,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,56; -0,69</t>
+          <t>-19,47; -1,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 7,01</t>
+          <t>-37,32; -0,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,23%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 7,64</t>
+          <t>-11,51; 7,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 4,4</t>
+          <t>-10,07; 4,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 12,5</t>
+          <t>-8,11; 12,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 7,38</t>
+          <t>-5,93; 10,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 29,88</t>
+          <t>-31,67; 29,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 5,36</t>
+          <t>-11,44; 5,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 25,77</t>
+          <t>-14,34; 24,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 44,88</t>
+          <t>-23,79; 62,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 12,01</t>
+          <t>-4,52; 12,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 9,29</t>
+          <t>-5,82; 9,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 11,56</t>
+          <t>-5,43; 12,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 9,28</t>
+          <t>-7,52; 9,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 44,38</t>
+          <t>-12,27; 45,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 12,23</t>
+          <t>-6,98; 12,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 17,8</t>
+          <t>-7,34; 18,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 35,98</t>
+          <t>-20,92; 35,7</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,54</t>
+          <t>-3,23</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-10,31%</t>
+          <t>-9,11%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,0</t>
+          <t>-4,05; 5,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 2,97</t>
+          <t>-4,91; 2,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 3,07</t>
+          <t>-6,43; 2,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 1,48</t>
+          <t>-8,6; 1,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 21,65</t>
+          <t>-11,9; 18,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 3,7</t>
+          <t>-5,79; 3,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 4,61</t>
+          <t>-8,95; 4,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,91; 4,58</t>
+          <t>-22,56; 4,96</t>
         </is>
       </c>
     </row>
